--- a/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D8D8B2-B6BA-4354-821B-176CAB5ED7B3}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D18B560-8B75-5516-85C6-D32C1119490E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -452,14 +452,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>10006309.090909099</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -609,7 +609,7 @@
         <v>29594363.636363599</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -659,7 +659,7 @@
         <v>3975669.9953232114</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -709,7 +709,7 @@
         <v>15648181.8181818</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -759,7 +759,7 @@
         <v>3813942.8082891181</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -809,7 +809,7 @@
         <v>2086489.1525458919</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -859,7 +859,7 @@
         <v>295238787.87878799</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -909,7 +909,7 @@
         <v>7420000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -959,7 +959,7 @@
         <v>63220606.0606061</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>36219272.727272697</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>9129696.9696969707</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>94921939.393939406</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>14653757.5757575</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>67934787.878787801</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1268,9 +1268,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1838,9 +1838,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2408,9 +2408,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2978,9 +2978,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3548,9 +3548,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4118,13 +4118,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
